--- a/ARM Functions/Move Edits/Ultima Cannon.xlsx
+++ b/ARM Functions/Move Edits/Ultima Cannon.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5B5310-1D9B-4425-BC81-E47DC2190CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237CA5B5-C2DF-477D-9EFE-814F123B6156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edit" sheetId="12" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="133">
   <si>
     <t>Address</t>
   </si>
@@ -272,9 +272,6 @@
     <t>bl 0x000876F8</t>
   </si>
   <si>
-    <t>mov r1, 0x5</t>
-  </si>
-  <si>
     <t>mov r1, 0x7</t>
   </si>
   <si>
@@ -305,45 +302,12 @@
     <t>bl 0x000D6F98</t>
   </si>
   <si>
-    <t>Get Pointer</t>
-  </si>
-  <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>sub r0, r0, 0x100</t>
-  </si>
-  <si>
-    <t>subs r0, 0x7C</t>
-  </si>
-  <si>
     <t>D4070000</t>
   </si>
   <si>
-    <t>000D0E0C</t>
-  </si>
-  <si>
     <t>30402DE9</t>
   </si>
   <si>
-    <t>4DDBFEEB</t>
-  </si>
-  <si>
-    <t>0A00001A</t>
-  </si>
-  <si>
-    <t>1805FFEB</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
-    <t>010C40E2</t>
-  </si>
-  <si>
-    <t>7C0050E2</t>
-  </si>
-  <si>
     <t>0300001A</t>
   </si>
   <si>
@@ -356,15 +320,9 @@
     <t>3040BDE8</t>
   </si>
   <si>
-    <t>BBC7FEEA</t>
-  </si>
-  <si>
     <t>3080BDE8</t>
   </si>
   <si>
-    <t>STAB if Latias 0x54</t>
-  </si>
-  <si>
     <t>Ultima Cannon Setup 0xB3</t>
   </si>
   <si>
@@ -423,13 +381,67 @@
   </si>
   <si>
     <t>000C8CE4</t>
+  </si>
+  <si>
+    <t>mov r1, 0x1</t>
+  </si>
+  <si>
+    <t>bl 0x00082D44</t>
+  </si>
+  <si>
+    <t>mov r0, 0x50</t>
+  </si>
+  <si>
+    <t>mov r0, 0x3D</t>
+  </si>
+  <si>
+    <t>0010257C</t>
+  </si>
+  <si>
+    <t>7115FEEB</t>
+  </si>
+  <si>
+    <t>0E00001A</t>
+  </si>
+  <si>
+    <t>6D15FEEB</t>
+  </si>
+  <si>
+    <t>3A3FFEEB</t>
+  </si>
+  <si>
+    <t>7952FFEB</t>
+  </si>
+  <si>
+    <t>0600001A</t>
+  </si>
+  <si>
+    <t>3D00A0E3</t>
+  </si>
+  <si>
+    <t>DF01FEEB</t>
+  </si>
+  <si>
+    <t>0110A0E3</t>
+  </si>
+  <si>
+    <t>5000A0E3</t>
+  </si>
+  <si>
+    <t>DB01FEEA</t>
+  </si>
+  <si>
+    <t>Ignore Type Effectiveness when attacking Mega/Ultra 0x4E/0x4F</t>
+  </si>
+  <si>
+    <t>mov r1, 0x6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -514,7 +526,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -538,8 +550,6 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -875,22 +885,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D33247EB-EDD1-4FB4-BA08-1D454B2F7DD3}">
-  <dimension ref="A1:I91"/>
-  <sheetFormatPr defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I95"/>
+  <sheetFormatPr defaultColWidth="9.2109375" defaultRowHeight="15.9"/>
   <cols>
-    <col min="1" max="1" width="11.53515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="35.61328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="89.765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.61328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.69140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.61328125" style="2" customWidth="1"/>
-    <col min="8" max="11" width="9.23046875" style="2"/>
-    <col min="12" max="12" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.23046875" style="2"/>
+    <col min="3" max="3" width="35.640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="89.78515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.640625" style="2" customWidth="1"/>
+    <col min="8" max="11" width="9.2109375" style="2"/>
+    <col min="12" max="12" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.2109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,7 +914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -912,20 +922,20 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
-        <v>0510A0E3</v>
+        <v>0610A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="str">
         <f t="shared" ref="A4:A7" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000C8CE8</v>
@@ -938,7 +948,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000C8CEC</v>
@@ -951,7 +961,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000C8CF0</v>
@@ -963,7 +973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000C8CF4</v>
@@ -975,19 +985,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>37</v>
@@ -996,7 +1006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="str">
         <f t="shared" ref="A11:A45" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
         <v>00101608</v>
@@ -1008,7 +1018,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0010160C</v>
@@ -1020,7 +1030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101610</v>
@@ -1032,7 +1042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4">
       <c r="A14" s="5" t="str">
         <f t="shared" si="1"/>
         <v>00101614</v>
@@ -1047,20 +1057,20 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4">
       <c r="A15" s="5" t="str">
         <f t="shared" si="1"/>
         <v>00101618</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4">
       <c r="A16" s="5" t="str">
         <f t="shared" si="1"/>
         <v>0010161C</v>
@@ -1073,13 +1083,13 @@
       </c>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4">
       <c r="A17" s="5" t="str">
         <f t="shared" si="1"/>
         <v>00101620</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C17" s="6" t="str">
         <f>_xlfn.CONCAT("bne 0x",A44)</f>
@@ -1087,7 +1097,7 @@
       </c>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4">
       <c r="A18" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00101624</v>
@@ -1102,20 +1112,20 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4">
       <c r="A19" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00101628</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4">
       <c r="A20" s="9" t="str">
         <f t="shared" si="1"/>
         <v>0010162C</v>
@@ -1128,20 +1138,20 @@
       </c>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4">
       <c r="A21" s="9" t="str">
         <f t="shared" si="1"/>
         <v>00101630</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>77</v>
       </c>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4">
       <c r="A22" s="12" t="str">
         <f t="shared" si="1"/>
         <v>00101634</v>
@@ -1156,7 +1166,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4">
       <c r="A23" s="12" t="str">
         <f t="shared" si="1"/>
         <v>00101638</v>
@@ -1169,7 +1179,7 @@
       </c>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4">
       <c r="A24" s="12" t="str">
         <f t="shared" si="1"/>
         <v>0010163C</v>
@@ -1182,7 +1192,7 @@
       </c>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4">
       <c r="A25" s="12" t="str">
         <f t="shared" si="1"/>
         <v>00101640</v>
@@ -1195,7 +1205,7 @@
       </c>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4">
       <c r="A26" s="12" t="str">
         <f t="shared" si="1"/>
         <v>00101644</v>
@@ -1208,26 +1218,26 @@
       </c>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4">
       <c r="A27" s="12" t="str">
         <f t="shared" si="1"/>
         <v>00101648</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4">
       <c r="A28" s="15" t="str">
         <f t="shared" si="1"/>
         <v>0010164C</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C28" s="17" t="str">
         <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A45)-HEX2DEC(A28)-8,"]")</f>
@@ -1237,7 +1247,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4">
       <c r="A29" s="15" t="str">
         <f t="shared" si="1"/>
         <v>00101650</v>
@@ -1250,7 +1260,7 @@
       </c>
       <c r="D29" s="15"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4">
       <c r="A30" s="15" t="str">
         <f t="shared" si="1"/>
         <v>00101654</v>
@@ -1263,20 +1273,20 @@
       </c>
       <c r="D30" s="15"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4">
       <c r="A31" s="15" t="str">
         <f t="shared" si="1"/>
         <v>00101658</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>43</v>
       </c>
       <c r="D31" s="15"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4">
       <c r="A32" s="15" t="str">
         <f t="shared" si="1"/>
         <v>0010165C</v>
@@ -1289,7 +1299,7 @@
       </c>
       <c r="D32" s="15"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9">
       <c r="A33" s="15" t="str">
         <f t="shared" si="1"/>
         <v>00101660</v>
@@ -1302,7 +1312,7 @@
       </c>
       <c r="D33" s="15"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9">
       <c r="A34" s="15" t="str">
         <f t="shared" si="1"/>
         <v>00101664</v>
@@ -1315,7 +1325,7 @@
       </c>
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9">
       <c r="A35" s="15" t="str">
         <f t="shared" si="1"/>
         <v>00101668</v>
@@ -1328,20 +1338,20 @@
       </c>
       <c r="D35" s="15"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9">
       <c r="A36" s="15" t="str">
         <f t="shared" si="1"/>
         <v>0010166C</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>44</v>
       </c>
       <c r="D36" s="15"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101670</v>
@@ -1353,7 +1363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9">
       <c r="A38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101674</v>
@@ -1365,19 +1375,19 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9">
       <c r="A39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101678</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0010167C</v>
@@ -1389,7 +1399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101680</v>
@@ -1401,7 +1411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9">
       <c r="A42" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101684</v>
@@ -1414,19 +1424,19 @@
         <v>pop {r4, r5, r6, r7, r8, lr}</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101688</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9">
       <c r="A44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0010168C</v>
@@ -1439,50 +1449,50 @@
         <v>pop {r4, r5, r6, r7, r8, pc}</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9">
       <c r="A45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101690</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I45" s="19"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="20"/>
       <c r="D50" s="18"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4">
       <c r="A51" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="2" t="str">
         <f t="shared" ref="A52:A70" si="2">DEC2HEX(HEX2DEC(A51)+4,8)</f>
         <v>00101698</v>
@@ -1494,7 +1504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4">
       <c r="A53" s="2" t="str">
         <f t="shared" si="2"/>
         <v>0010169C</v>
@@ -1506,7 +1516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4">
       <c r="A54" s="5" t="str">
         <f t="shared" si="2"/>
         <v>001016A0</v>
@@ -1521,20 +1531,20 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4">
       <c r="A55" s="5" t="str">
         <f t="shared" si="2"/>
         <v>001016A4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D55" s="5"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4">
       <c r="A56" s="5" t="str">
         <f t="shared" si="2"/>
         <v>001016A8</v>
@@ -1547,13 +1557,13 @@
       </c>
       <c r="D56" s="5"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4">
       <c r="A57" s="5" t="str">
         <f t="shared" si="2"/>
         <v>001016AC</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C57" s="6" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$70)</f>
@@ -1561,7 +1571,7 @@
       </c>
       <c r="D57" s="5"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4">
       <c r="A58" s="21" t="str">
         <f t="shared" si="2"/>
         <v>001016B0</v>
@@ -1573,23 +1583,23 @@
         <v>71</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" s="21" t="str">
         <f t="shared" si="2"/>
         <v>001016B4</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C59" s="22" t="s">
         <v>69</v>
       </c>
       <c r="D59" s="21"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4">
       <c r="A60" s="21" t="str">
         <f t="shared" si="2"/>
         <v>001016B8</v>
@@ -1602,7 +1612,7 @@
       </c>
       <c r="D60" s="21"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4">
       <c r="A61" s="21" t="str">
         <f t="shared" si="2"/>
         <v>001016BC</v>
@@ -1615,153 +1625,151 @@
       </c>
       <c r="D61" s="21"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4">
       <c r="A62" s="21" t="str">
         <f t="shared" si="2"/>
         <v>001016C0</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C62" s="21" t="s">
         <v>74</v>
       </c>
       <c r="D62" s="21"/>
     </row>
-    <row r="63" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="23" t="str">
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016C4</v>
       </c>
-      <c r="B63" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" s="23" t="str">
+      <c r="B63" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016C8</v>
       </c>
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D64" s="23"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" s="23" t="str">
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016CC</v>
       </c>
-      <c r="B65" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" s="23" t="str">
+      <c r="B65" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="2" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$70)</f>
         <v>bne 0x001016E0</v>
       </c>
-      <c r="D65" s="23"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="23" t="str">
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016D0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="23" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016D4</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="23" t="str">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016D8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C68" s="2" t="str">
         <f>SUBSTITUTE(C51,"push","pop")</f>
         <v>pop {r4, r5, lr}</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="23" t="str">
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016DC</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="23" t="str">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2" t="str">
         <f t="shared" si="2"/>
         <v>001016E0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C70" s="2" t="str">
         <f>SUBSTITUTE(C68,"lr","pc")</f>
         <v>pop {r4, r5, pc}</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B72" s="20"/>
       <c r="D72" s="18"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="2" t="s">
-        <v>94</v>
+    <row r="73" spans="1:4">
+      <c r="A73" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="2" t="str">
-        <f t="shared" ref="A74:A91" si="3">DEC2HEX(HEX2DEC(A73)+4,8)</f>
-        <v>000D0E10</v>
+        <f t="shared" ref="A74:A95" si="3">DEC2HEX(HEX2DEC(A73)+4,8)</f>
+        <v>00102580</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>29</v>
@@ -1770,10 +1778,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4">
       <c r="A75" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E14</v>
+        <v>00102584</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -1782,10 +1790,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4">
       <c r="A76" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E18</v>
+        <v>00102588</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>16</v>
@@ -1797,23 +1805,23 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4">
       <c r="A77" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E1C</v>
+        <v>0010258C</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D77" s="5"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4">
       <c r="A78" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E20</v>
+        <v>00102590</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>33</v>
@@ -1823,182 +1831,224 @@
       </c>
       <c r="D78" s="5"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4">
       <c r="A79" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E24</v>
+        <v>00102594</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="C79" s="6" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A91)</f>
-        <v>bne 0x000D0E54</v>
+        <f>_xlfn.CONCAT("bne 0x",A$95)</f>
+        <v>bne 0x001025D4</v>
       </c>
       <c r="D79" s="5"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4">
       <c r="A80" s="21" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E28</v>
+        <v>00102598</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="21" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E2C</v>
+        <v>0010259C</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>73</v>
+        <v>122</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="D81" s="21"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4">
       <c r="A82" s="21" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E30</v>
+        <v>001025A0</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="C82" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="21"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>001025A4</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D83" s="21"/>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v>001025A8</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C84" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D82" s="21"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A83" s="23" t="str">
+      <c r="D84" s="21"/>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E34</v>
-      </c>
-      <c r="B83" s="23" t="s">
+        <v>001025AC</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>001025B0</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>001025B4</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C87" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$95)</f>
+        <v>bne 0x001025D4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>001025B8</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D83" s="23"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A84" s="23" t="str">
+      <c r="C88" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E38</v>
-      </c>
-      <c r="B84" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D84" s="23"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A85" s="23" t="str">
+        <v>001025BC</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E3C</v>
-      </c>
-      <c r="B85" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C85" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D85" s="23"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A86" s="23" t="str">
+        <v>001025C0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E40</v>
-      </c>
-      <c r="B86" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C86" s="23" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A91)</f>
-        <v>bne 0x000D0E54</v>
-      </c>
-      <c r="D86" s="23"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A87" s="23" t="str">
+        <v>001025C4</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E44</v>
-      </c>
-      <c r="B87" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C87" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D87" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A88" s="23" t="str">
+        <v>001025C8</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E48</v>
-      </c>
-      <c r="B88" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D88" s="23"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A89" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v>000D0E4C</v>
-      </c>
-      <c r="B89" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C89" s="23" t="str">
+        <v>001025CC</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C93" s="2" t="str">
         <f>SUBSTITUTE(C73,"push","pop")</f>
         <v>pop {r4, r5, lr}</v>
       </c>
-      <c r="D89" s="23"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A90" s="23" t="str">
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E50</v>
-      </c>
-      <c r="B90" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="C90" s="23" t="s">
+        <v>001025D0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D90" s="23"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A91" s="23" t="str">
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D0E54</v>
-      </c>
-      <c r="B91" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C91" s="23" t="str">
-        <f>SUBSTITUTE(C89,"lr","pc")</f>
+        <v>001025D4</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C95" s="2" t="str">
+        <f>SUBSTITUTE(C93,"lr","pc")</f>
         <v>pop {r4, r5, pc}</v>
       </c>
-      <c r="D91" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ARM Functions/Move Edits/Ultima Cannon.xlsx
+++ b/ARM Functions/Move Edits/Ultima Cannon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237CA5B5-C2DF-477D-9EFE-814F123B6156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E655DF-D666-4F20-A9F4-A928DAE9579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edit" sheetId="12" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="152">
   <si>
     <t>Address</t>
   </si>
@@ -170,21 +170,12 @@
     <t>bl 0x000876f8</t>
   </si>
   <si>
-    <t>bl 0x00089c6c</t>
-  </si>
-  <si>
-    <t>bl 0x0007f804</t>
-  </si>
-  <si>
     <t>add r0, r0, 0x4</t>
   </si>
   <si>
     <t>Self attacker</t>
   </si>
   <si>
-    <t>mov r2, r8</t>
-  </si>
-  <si>
     <t>mov r7, r0</t>
   </si>
   <si>
@@ -212,9 +203,6 @@
     <t>mov r5, r0</t>
   </si>
   <si>
-    <t>print text</t>
-  </si>
-  <si>
     <t>add r0, r5, 0x4</t>
   </si>
   <si>
@@ -239,9 +227,6 @@
     <t>0050A0E1</t>
   </si>
   <si>
-    <t>0820A0E1</t>
-  </si>
-  <si>
     <t>040085E2</t>
   </si>
   <si>
@@ -278,15 +263,6 @@
     <t>get pointer to defender</t>
   </si>
   <si>
-    <t>1.5x damage</t>
-  </si>
-  <si>
-    <t>mov r1, 0x1800</t>
-  </si>
-  <si>
-    <t>1.5x damage against Ultra Bursted and Mega Evolved Pokemon 0x5B</t>
-  </si>
-  <si>
     <t>mov r0, 0x39</t>
   </si>
   <si>
@@ -311,9 +287,6 @@
     <t>0300001A</t>
   </si>
   <si>
-    <t>061BA0E3</t>
-  </si>
-  <si>
     <t>3900A0E3</t>
   </si>
   <si>
@@ -344,9 +317,6 @@
     <t>A9EDFDEB</t>
   </si>
   <si>
-    <t>BC23DFE1</t>
-  </si>
-  <si>
     <t>2618FEEB</t>
   </si>
   <si>
@@ -434,7 +404,94 @@
     <t>Ignore Type Effectiveness when attacking Mega/Ultra 0x4E/0x4F</t>
   </si>
   <si>
+    <t>mov r1, 0x19</t>
+  </si>
+  <si>
+    <t>Get pointer for text</t>
+  </si>
+  <si>
+    <t>bl 0x00089C6C</t>
+  </si>
+  <si>
+    <t>Get text string</t>
+  </si>
+  <si>
+    <t>bl 0x0007F804</t>
+  </si>
+  <si>
+    <t>Print text</t>
+  </si>
+  <si>
+    <t>Ignore Protect 0x3B</t>
+  </si>
+  <si>
+    <t>000CE184</t>
+  </si>
+  <si>
+    <t>1910A0E3</t>
+  </si>
+  <si>
+    <t>B822DFE1</t>
+  </si>
+  <si>
+    <t>2x damage against Ultra Bursted and Mega Evolved Pokemon 0x5B</t>
+  </si>
+  <si>
+    <t>mov r0, 0x1C</t>
+  </si>
+  <si>
+    <t>add r1, r0, 0x2</t>
+  </si>
+  <si>
+    <t>Get current priority and add 2</t>
+  </si>
+  <si>
+    <t>001025D8</t>
+  </si>
+  <si>
+    <t>5A15FEEB</t>
+  </si>
+  <si>
+    <t>0D00001A</t>
+  </si>
+  <si>
+    <t>5615FEEB</t>
+  </si>
+  <si>
+    <t>233FFEEB</t>
+  </si>
+  <si>
+    <t>6252FFEB</t>
+  </si>
+  <si>
+    <t>0500001A</t>
+  </si>
+  <si>
+    <t>1C00A0E3</t>
+  </si>
+  <si>
+    <t>4E15FEEB</t>
+  </si>
+  <si>
+    <t>021080E2</t>
+  </si>
+  <si>
+    <t>C501FEEA</t>
+  </si>
+  <si>
+    <t>+2 Priority against Mega/Ultra/Primal Pokemon 0x11 (doesn't work, 0x11 won't run for Moves)</t>
+  </si>
+  <si>
     <t>mov r1, 0x6</t>
+  </si>
+  <si>
+    <t>031AA0E3</t>
+  </si>
+  <si>
+    <t>mov r1, 0x3000</t>
+  </si>
+  <si>
+    <t>3x damage</t>
   </si>
 </sst>
 </file>
@@ -475,7 +532,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,7 +565,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,7 +601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -542,14 +617,23 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D33247EB-EDD1-4FB4-BA08-1D454B2F7DD3}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr defaultColWidth="9.2109375" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
@@ -924,14 +1008,14 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
         <v>0610A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -992,12 +1076,12 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>37</v>
@@ -1012,10 +1096,10 @@
         <v>00101608</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1054,7 +1138,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1063,10 +1147,10 @@
         <v>00101618</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D15" s="5"/>
     </row>
@@ -1089,7 +1173,7 @@
         <v>00101620</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C17" s="6" t="str">
         <f>_xlfn.CONCAT("bne 0x",A44)</f>
@@ -1109,7 +1193,7 @@
         <v>21</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1118,10 +1202,10 @@
         <v>00101628</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D19" s="9"/>
     </row>
@@ -1144,10 +1228,10 @@
         <v>00101630</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D21" s="9"/>
     </row>
@@ -1163,7 +1247,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1172,10 +1256,10 @@
         <v>00101638</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D23" s="12"/>
     </row>
@@ -1185,10 +1269,10 @@
         <v>0010163C</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D24" s="12"/>
     </row>
@@ -1198,10 +1282,10 @@
         <v>00101640</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D25" s="12"/>
     </row>
@@ -1224,192 +1308,201 @@
         <v>00101648</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0010164C</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>00101650</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="20"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>00101654</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="20"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>00101658</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="20"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0010165C</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="20"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00101660</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="25" t="str">
+        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A45)-HEX2DEC(A33)-8,"]")</f>
+        <v>ldrh r2, [pc, #40]</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00101664</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="23"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00101668</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="23"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0010166C</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="23"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>00101670</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="26"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>00101674</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="12"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>0010164C</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="17" t="str">
-        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A45)-HEX2DEC(A28)-8,"]")</f>
-        <v>ldrh r2, [pc, #60]</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101650</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="15"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101654</v>
-      </c>
-      <c r="B30" s="16" t="s">
+      <c r="D38" s="26"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>00101678</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="26"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>0010167C</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>00101680</v>
+      </c>
+      <c r="B41" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C41" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="15"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101658</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="15"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>0010165C</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="15"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101660</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101664</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="15"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>00101668</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>0010166C</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="15"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101670</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101674</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101678</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>0010167C</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101680</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="D41" s="29"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2" t="str">
@@ -1419,22 +1512,23 @@
       <c r="B42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="18" t="str">
+      <c r="C42" s="15" t="str">
         <f>SUBSTITUTE(C10,"push","pop")</f>
         <v>pop {r4, r5, r6, r7, r8, lr}</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="2" t="str">
+      <c r="A43" s="29" t="str">
         <f t="shared" si="1"/>
         <v>00101688</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B43" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="29" t="s">
         <v>23</v>
       </c>
+      <c r="D43" s="29"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="str">
@@ -1455,18 +1549,18 @@
         <v>00101690</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I45" s="19"/>
+        <v>80</v>
+      </c>
+      <c r="I45" s="16"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1476,20 +1570,20 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="20"/>
-      <c r="D50" s="18"/>
+        <v>132</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="D50" s="15"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1528,7 +1622,7 @@
         <v>13</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1537,10 +1631,10 @@
         <v>001016A4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D55" s="5"/>
     </row>
@@ -1563,7 +1657,7 @@
         <v>001016AC</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C57" s="6" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$70)</f>
@@ -1572,71 +1666,71 @@
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="21" t="str">
+      <c r="A58" s="18" t="str">
         <f t="shared" si="2"/>
         <v>001016B0</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>79</v>
+      <c r="B58" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="21" t="str">
+      <c r="A59" s="18" t="str">
         <f t="shared" si="2"/>
         <v>001016B4</v>
       </c>
-      <c r="B59" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D59" s="21"/>
+      <c r="B59" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" s="18"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="21" t="str">
+      <c r="A60" s="18" t="str">
         <f t="shared" si="2"/>
         <v>001016B8</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="21"/>
+      <c r="D60" s="18"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="21" t="str">
+      <c r="A61" s="18" t="str">
         <f t="shared" si="2"/>
         <v>001016BC</v>
       </c>
-      <c r="B61" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" s="21"/>
+      <c r="B61" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="18"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="21" t="str">
+      <c r="A62" s="18" t="str">
         <f t="shared" si="2"/>
         <v>001016C0</v>
       </c>
-      <c r="B62" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" s="21"/>
+      <c r="B62" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="18"/>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="str">
@@ -1644,13 +1738,13 @@
         <v>001016C4</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1659,10 +1753,10 @@
         <v>001016C8</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1671,7 +1765,7 @@
         <v>001016CC</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C65" s="2" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$70)</f>
@@ -1684,13 +1778,13 @@
         <v>001016D0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1699,10 +1793,10 @@
         <v>001016D4</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1711,7 +1805,7 @@
         <v>001016D8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C68" s="2" t="str">
         <f>SUBSTITUTE(C51,"push","pop")</f>
@@ -1724,10 +1818,10 @@
         <v>001016DC</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1736,7 +1830,7 @@
         <v>001016E0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C70" s="2" t="str">
         <f>SUBSTITUTE(C68,"lr","pc")</f>
@@ -1750,20 +1844,20 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B72" s="20"/>
-      <c r="D72" s="18"/>
+        <v>121</v>
+      </c>
+      <c r="B72" s="17"/>
+      <c r="D72" s="15"/>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1802,7 +1896,7 @@
         <v>13</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1811,10 +1905,10 @@
         <v>0010258C</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D77" s="5"/>
     </row>
@@ -1837,7 +1931,7 @@
         <v>00102594</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C79" s="6" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$95)</f>
@@ -1846,71 +1940,71 @@
       <c r="D79" s="5"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="21" t="str">
+      <c r="A80" s="18" t="str">
         <f t="shared" si="3"/>
         <v>00102598</v>
       </c>
-      <c r="B80" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>79</v>
+      <c r="B80" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="21" t="str">
+      <c r="A81" s="18" t="str">
         <f t="shared" si="3"/>
         <v>0010259C</v>
       </c>
-      <c r="B81" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D81" s="21"/>
+      <c r="B81" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D81" s="18"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="21" t="str">
+      <c r="A82" s="18" t="str">
         <f t="shared" si="3"/>
         <v>001025A0</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D82" s="21"/>
+      <c r="D82" s="18"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="21" t="str">
+      <c r="A83" s="18" t="str">
         <f t="shared" si="3"/>
         <v>001025A4</v>
       </c>
-      <c r="B83" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D83" s="21"/>
+      <c r="B83" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" s="18"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="21" t="str">
+      <c r="A84" s="18" t="str">
         <f t="shared" si="3"/>
         <v>001025A8</v>
       </c>
-      <c r="B84" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D84" s="21"/>
+      <c r="B84" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" s="18"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2" t="str">
@@ -1918,13 +2012,13 @@
         <v>001025AC</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1933,10 +2027,10 @@
         <v>001025B0</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1945,7 +2039,7 @@
         <v>001025B4</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C87" s="2" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$95)</f>
@@ -1958,10 +2052,10 @@
         <v>001025B8</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1970,10 +2064,10 @@
         <v>001025BC</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1982,10 +2076,10 @@
         <v>001025C0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1994,10 +2088,10 @@
         <v>001025C4</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2006,10 +2100,10 @@
         <v>001025C8</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2018,7 +2112,7 @@
         <v>001025CC</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C93" s="2" t="str">
         <f>SUBSTITUTE(C73,"push","pop")</f>
@@ -2031,7 +2125,7 @@
         <v>001025D0</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>14</v>
@@ -2043,10 +2137,315 @@
         <v>001025D4</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C95" s="2" t="str">
         <f>SUBSTITUTE(C93,"lr","pc")</f>
+        <v>pop {r4, r5, pc}</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B100" s="17"/>
+      <c r="D100" s="15"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="2" t="str">
+        <f t="shared" ref="A102:A122" si="4">DEC2HEX(HEX2DEC(A101)+4,8)</f>
+        <v>001025DC</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>001025E0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>001025E4</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>001025E8</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D105" s="5"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>001025EC</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D106" s="5"/>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>001025F0</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C107" s="6" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A122)</f>
+        <v>bne 0x0010262C</v>
+      </c>
+      <c r="D107" s="5"/>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>001025F4</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D108" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>001025F8</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D109" s="18"/>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>001025FC</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="18"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>00102600</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" s="18"/>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18" t="str">
+        <f t="shared" si="4"/>
+        <v>00102604</v>
+      </c>
+      <c r="B112" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D112" s="18"/>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>00102608</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0010260C</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>00102610</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C115" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A122)</f>
+        <v>bne 0x0010262C</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>00102614</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>00102618</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D117" s="9"/>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>0010261C</v>
+      </c>
+      <c r="B118" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D118" s="9"/>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>00102620</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>00102624</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C120" s="2" t="str">
+        <f>SUBSTITUTE(C101,"push","pop")</f>
+        <v>pop {r4, r5, lr}</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>00102628</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0010262C</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C122" s="2" t="str">
+        <f>SUBSTITUTE(C120,"lr","pc")</f>
         <v>pop {r4, r5, pc}</v>
       </c>
     </row>
